--- a/physical_location_labelling/physical_location_by_context/v03_gpt_annotation/results/gpt_1000_output_analysis.xlsx
+++ b/physical_location_labelling/physical_location_by_context/v03_gpt_annotation/results/gpt_1000_output_analysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eestikeeleinstituut-my.sharepoint.com/personal/kertu_saul_eki_ee/Documents/Dokumendid/doktoritoo/estnltk_syntax_repo_kloon/physical_location_labelling/physical_location_by_context/results/v03_gpt_annotation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eestikeeleinstituut-my.sharepoint.com/personal/kertu_saul_eki_ee/Documents/Dokumendid/doktoritoo/estnltk_syntax_repo_kloon/physical_location_labelling/physical_location_by_context/v03_gpt_annotation/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="356" documentId="8_{BEC30906-46EE-4C43-A66A-D354C8275BEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37985EBD-E2F8-48A9-914C-06F8A94839FC}"/>
+  <xr:revisionPtr revIDLastSave="364" documentId="8_{BEC30906-46EE-4C43-A66A-D354C8275BEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26EDDF5E-1502-4CEE-82E9-58D6E2C4F54C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{C390DCA3-6CE8-4683-AFF8-BA98244D7D99}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C390DCA3-6CE8-4683-AFF8-BA98244D7D99}"/>
   </bookViews>
   <sheets>
     <sheet name="kohad_1000_gpt_väljund" sheetId="2" r:id="rId1"/>
@@ -6300,7 +6300,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[kohad_1000_gpt_valjund_excel.xlsx]FN_count!PivotTable15</c:name>
+    <c:name>[gpt_1000_output_analysis.xlsx]FN_count!PivotTable15</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -6704,7 +6704,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[kohad_1000_gpt_valjund_excel.xlsx]vea_statistika!PivotTable15</c:name>
+    <c:name>[gpt_1000_output_analysis.xlsx]vea_statistika!PivotTable15</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -7144,7 +7144,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[kohad_1000_gpt_valjund_excel.xlsx]FP_count!PivotTable10</c:name>
+    <c:name>[gpt_1000_output_analysis.xlsx]FP_count!PivotTable10</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -43314,7 +43314,7 @@
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" customWidth="1"/>
+    <col min="1" max="1" width="64.33203125" customWidth="1"/>
     <col min="5" max="5" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -43335,7 +43335,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="78" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>174</v>
       </c>
@@ -43369,7 +43369,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>304</v>
       </c>
@@ -43403,7 +43403,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>402</v>
       </c>
@@ -43505,7 +43505,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>1124</v>
       </c>
@@ -43624,7 +43624,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>1862</v>
       </c>
@@ -43711,6 +43711,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -44008,6 +44009,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAE54407-7133-4087-A659-C31C92623B51}">
   <dimension ref="A1:E88"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="32.44140625" customWidth="1"/>
+    <col min="3" max="3" width="26.5546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
